--- a/10_Trade_Finance/_template_TRADE_FINANCE.xlsx
+++ b/10_Trade_Finance/_template_TRADE_FINANCE.xlsx
@@ -11,7 +11,8 @@
     <sheet name="Cover" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Working Capital Cycle" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="LC &amp; Factoring Cost" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="RefreshLog" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Financing Cost Comparison" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="RefreshLog" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t xml:space="preserve">[COUNTERPARTY] — Trade Finance Model</t>
   </si>
@@ -146,6 +147,63 @@
   </si>
   <si>
     <t xml:space="preserve">Compare vs. bank credit line rate to decide financing channel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which Financing Channel Is Cheapest?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revolving credit line (alternative)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw amount ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base rate + spread, all-in (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commitment fee on undrawn (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Undrawn facility amount ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revolver interest cost ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revolver commitment fee ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revolver annualized all-in cost %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Channel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annualized cost %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Letter of credit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factoring / invoice discounting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revolving credit line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheapest channel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only declares a winner once all three channels have real numbers — one live rate shouldn't beat two blanks by default</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheapest annualized cost %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compares only financing cost — also weigh speed, collateral/covenant burden, and counterparty credit risk transfer (LC shifts payment risk to the issuing bank; factoring can be non-recourse)</t>
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
@@ -170,14 +228,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="168" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="169" formatCode="0.00%;\(0.00%\);\-"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -244,6 +303,13 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -320,7 +386,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -382,11 +448,23 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -646,7 +724,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -708,7 +786,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:D16"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -836,7 +914,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:D21"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -996,8 +1074,166 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:D20"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <f aca="false">C5*C6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <f aca="false">C7*C8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="14" t="str">
+        <f aca="false">IFERROR((C9+C10)/C5,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="18" t="str">
+        <f aca="false">'LC &amp; Factoring Cost'!C10</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <f aca="false">'LC &amp; Factoring Cost'!C21</f>
+        <v>0.121666666666667</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="18" t="str">
+        <f aca="false">C11</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="19" t="str">
+        <f aca="false">IF(COUNT(C15:C17)&lt;3,"-",INDEX(B15:B17,MATCH(MIN(C15:C17),C15:C17,0)))</f>
+        <v>-</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="15" t="str">
+        <f aca="false">IF(COUNT(C15:C17)&lt;3,"-",MIN(C15:C17))</f>
+        <v>-</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:F14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
@@ -1008,95 +1244,95 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>46</v>
+      <c r="B4" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
